--- a/sample_data/new_coverage.xlsx
+++ b/sample_data/new_coverage.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="115">
   <si>
     <t>담보코드</t>
   </si>
@@ -49,6 +49,9 @@
     <t>CV0002</t>
   </si>
   <si>
+    <t>CV0008</t>
+  </si>
+  <si>
     <t>CV0007</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>질병 심장보장</t>
   </si>
   <si>
+    <t>질병 간병보장</t>
+  </si>
+  <si>
     <t>상해 골절보장</t>
   </si>
   <si>
@@ -184,124 +190,94 @@
     <t>TK9030</t>
   </si>
   <si>
-    <t>TK9031</t>
-  </si>
-  <si>
-    <t>TK9032</t>
-  </si>
-  <si>
-    <t>TK9033</t>
-  </si>
-  <si>
-    <t>TK9034</t>
-  </si>
-  <si>
-    <t>TK9035</t>
-  </si>
-  <si>
     <t>(무)통풍진단특약Ⅱ(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)통풍진단특약Ⅱ(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)통풍진단특약Ⅱ(갱신형)(간편심사형)</t>
-  </si>
-  <si>
     <t>(무)간경변증진단특약(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)간경변증진단특약(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)간경변증진단특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
     <t>R(무)5대장기이식수술특약(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)5대장기이식수술특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
     <t>(무)뇌전증진단특약(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)뇌전증진단특약(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)뇌전증진단특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
     <t>R(무)대동맥인조혈관치환수술특약(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)대동맥인조혈관치환수술특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
     <t>R(무)고액암진단특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)암산정특례대상보장특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)암직접치료상급종합병원통원특약Ⅱ(갱신형)(간편심사형)</t>
+    <t>R(무)소액암진단특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)암직접치료(요양병원제외)입원특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)암직접치료종합병원통원특약(연간30회)(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)일반암진단특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)항암중입자방사선치료특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)급성심근경색증혈전용해치료특약(갱신형)(간편심사형)</t>
+    <t>R(무)항암약물치료특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)급성뇌경색증혈전용해치료특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)뇌졸중진단특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)뇌혈관질환상급종합병원통원특약(연간30회)(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)뇌혈관질환진단특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)심장판막수술특약(갱신형)(간편심사형)</t>
+    <t>R(무)뇌혈관질환종합병원통원특약(연간30회)(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)부정맥진단특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)허혈성심장질환상급종합병원통원특약(연간30회)(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)허혈성심장질환종합병원통원특약(연간30회)(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)3대기관양성신생물및용종수술특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)응급실내원특약(갱신형)(간편심사형)</t>
+    <t>R(무)1~5종수술특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)갑상선기능항진증치료특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)입원간병인사용(요양병원)특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)재해골절치료특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)재해장해(50%이상)보장특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)질병장해(80%이상)보장특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)첫날부터입원(1~30일)특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)상급종합병원질병수술(백내장 및 대장용종 제외)특약(갱신형)(간편심사형)</t>
+    <t>R(무)재해장해(3~100%)보장특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)질병장해(3~100%)보장특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)첫날부터상급종합병원입원(1~120일)특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)급여암자기공명영상진단(MRI)검사지원특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>(무)허혈성심장질환입원특약(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)일반암납입면제특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)갑상선기능항진증치료특약(간편심사형)</t>
-  </si>
-  <si>
-    <t>R(무)급성뇌경색증혈전용해치료특약(갱신형)(간편심사형)</t>
+    <t>(무)허혈성심장질환수술특약(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)뇌졸중납입면제특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)1~5종수술특약(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)항암방사선치료특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>질병</t>
@@ -331,58 +307,58 @@
     <t>고액암</t>
   </si>
   <si>
-    <t>암</t>
-  </si>
-  <si>
-    <t>상급종합병원</t>
+    <t>소액암</t>
+  </si>
+  <si>
+    <t>암직접치료</t>
+  </si>
+  <si>
+    <t>종합병원</t>
   </si>
   <si>
     <t>일반암</t>
   </si>
   <si>
-    <t>중입자</t>
-  </si>
-  <si>
-    <t>급성심근경색</t>
+    <t>항암약물</t>
+  </si>
+  <si>
+    <t>급성뇌경색증</t>
+  </si>
+  <si>
+    <t>뇌졸중</t>
   </si>
   <si>
     <t>뇌혈관질환</t>
   </si>
   <si>
-    <t>심장판막</t>
+    <t>부정맥</t>
   </si>
   <si>
     <t>허혈성심장질환</t>
   </si>
   <si>
-    <t>양성신생물및용종</t>
-  </si>
-  <si>
-    <t>응급실내원</t>
+    <t>1~5종</t>
+  </si>
+  <si>
+    <t>갑상선기능항진증</t>
+  </si>
+  <si>
+    <t>요양병원</t>
   </si>
   <si>
     <t>골절</t>
   </si>
   <si>
-    <t>50%이상</t>
-  </si>
-  <si>
-    <t>80%이상</t>
-  </si>
-  <si>
-    <t>첫날입원</t>
-  </si>
-  <si>
-    <t>상급종합병원질병수술</t>
+    <t>3~100%</t>
+  </si>
+  <si>
+    <t>상급종합병원입원</t>
   </si>
   <si>
     <t>MRI</t>
   </si>
   <si>
-    <t>갑상선기능항진증</t>
-  </si>
-  <si>
-    <t>급성뇌경색증</t>
+    <t>일반방사선</t>
   </si>
 </sst>
 </file>
@@ -714,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -742,19 +718,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -762,19 +738,19 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -782,216 +758,216 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" t="s">
         <v>96</v>
-      </c>
-      <c r="F7" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
         <v>103</v>
@@ -999,19 +975,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
         <v>104</v>
@@ -1019,422 +995,322 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F29" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F30" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F31" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" t="s">
-        <v>96</v>
-      </c>
-      <c r="F32" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" t="s">
-        <v>96</v>
-      </c>
-      <c r="F33" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" t="s">
-        <v>93</v>
-      </c>
-      <c r="E34" t="s">
-        <v>98</v>
-      </c>
-      <c r="F34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" t="s">
-        <v>94</v>
-      </c>
-      <c r="E35" t="s">
-        <v>96</v>
-      </c>
-      <c r="F35" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" t="s">
-        <v>60</v>
-      </c>
-      <c r="D36" t="s">
-        <v>95</v>
-      </c>
-      <c r="E36" t="s">
-        <v>96</v>
-      </c>
-      <c r="F36" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
